--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487536_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487536_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9036</v>
+        <v>6.1827</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8462</v>
+        <v>4.2322</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0575</v>
+        <v>1.9506</v>
       </c>
       <c r="G2" t="n">
         <v>3.4638</v>
@@ -610,13 +610,13 @@
         <v>1.7626</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4779</v>
+        <v>0.7569</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9357</v>
+        <v>0.3217</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5422</v>
+        <v>0.4352</v>
       </c>
       <c r="V2" t="n">
         <v>2.1578</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5811</v>
+        <v>5.8404</v>
       </c>
       <c r="E3" t="n">
-        <v>7.4432</v>
+        <v>8.568899999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.8621</v>
+        <v>-2.7285</v>
       </c>
       <c r="G3" t="n">
         <v>4.7461</v>
@@ -688,13 +688,13 @@
         <v>2.546</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3412</v>
+        <v>-0.0819</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0516</v>
+        <v>0.0741</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2897</v>
+        <v>-0.156</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3905</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7022</v>
+        <v>2.2172</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5963</v>
+        <v>3.0846</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8941</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>1.5167</v>
@@ -766,13 +766,13 @@
         <v>0.9792</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0324</v>
+        <v>0.5474</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6693</v>
+        <v>0.1576</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3631</v>
+        <v>0.3898</v>
       </c>
       <c r="V4" t="n">
         <v>-0.8260999999999999</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9939</v>
+        <v>1.5194</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0185</v>
+        <v>2.2231</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0245</v>
+        <v>-0.7038</v>
       </c>
       <c r="G5" t="n">
         <v>1.979</v>
@@ -844,13 +844,13 @@
         <v>0.5875</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3561</v>
+        <v>0.1694</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3564</v>
+        <v>-0.1517</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0004</v>
+        <v>0.3211</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2166</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0535</v>
+        <v>-0.0001</v>
       </c>
       <c r="E6" t="n">
         <v>-0.0784</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0249</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>-1.1814</v>
@@ -922,13 +922,13 @@
         <v>0.1958</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5991</v>
+        <v>0.6525</v>
       </c>
       <c r="T6" t="n">
         <v>0.5634</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0356</v>
+        <v>0.0891</v>
       </c>
       <c r="V6" t="n">
         <v>0.3329</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. REY MARIÑO</t>
+          <t>A. MONTEAGUDO FERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2816</v>
+        <v>-0.1575</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5328000000000001</v>
+        <v>1.5107</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2512</v>
+        <v>-1.6682</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4773</v>
+        <v>1.278</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.346</v>
+        <v>1.3184</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1313</v>
+        <v>-0.0404</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0612</v>
+        <v>3.4279</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0612</v>
+        <v>2.8121</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.6159</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5385</v>
+        <v>-2.1499</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4073</v>
+        <v>-1.4936</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1313</v>
+        <v>-0.6563</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3917</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5875</v>
+        <v>0.9792</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5874</v>
+        <v>-0.7316</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3852</v>
+        <v>-0.2341</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2021</v>
+        <v>-0.4976</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. SANTORUM OTERO</t>
+          <t>D. REY MARIÑO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3333</v>
+        <v>-0.4107</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2032</v>
+        <v>-0.6351</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5365</v>
+        <v>0.2244</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3834</v>
+        <v>-0.4773</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7524</v>
+        <v>-0.346</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3689</v>
+        <v>-0.1313</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5762</v>
+        <v>0.0612</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3441</v>
+        <v>0.0612</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7679</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8073</v>
+        <v>-0.5385</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4083</v>
+        <v>-0.4073</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.399</v>
+        <v>-0.1313</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7834</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7834</v>
+        <v>0.5875</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2668</v>
+        <v>0.4583</v>
       </c>
       <c r="T8" t="n">
-        <v>0.504</v>
+        <v>0.2829</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2373</v>
+        <v>0.1754</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MONTEAGUDO FERNANDEZ</t>
+          <t>R. SANTORUM OTERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3759</v>
+        <v>-0.5868</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6131</v>
+        <v>-0.1038</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.989</v>
+        <v>-0.483</v>
       </c>
       <c r="G9" t="n">
-        <v>1.278</v>
+        <v>-1.3834</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3184</v>
+        <v>-1.7524</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0404</v>
+        <v>0.3689</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4279</v>
+        <v>-0.5762</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8121</v>
+        <v>-1.3441</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6159</v>
+        <v>0.7679</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1499</v>
+        <v>-0.8073</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4936</v>
+        <v>-0.4083</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6563</v>
+        <v>-0.399</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9792</v>
+        <v>0.7834</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9792</v>
+        <v>0.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9500999999999999</v>
+        <v>0.0132</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1317</v>
+        <v>0.197</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8183</v>
+        <v>-0.1838</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0.2754</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. GIL RODRIGUEZ</t>
+          <t>J. RODRIGUEZ BUCETA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1491</v>
+        <v>-2.5429</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.864</v>
+        <v>-4.0389</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7149</v>
+        <v>1.496</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1683</v>
+        <v>-2.002</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9766</v>
+        <v>-2.2144</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8083</v>
+        <v>0.2125</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2881</v>
+        <v>-1.404</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4004</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1123</v>
+        <v>-0.4802</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1198</v>
+        <v>-0.5979</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4239</v>
+        <v>-1.2905</v>
       </c>
       <c r="O10" t="n">
-        <v>0.304</v>
+        <v>0.6926</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.546</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.8962</v>
+        <v>-2.9377</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3502</v>
+        <v>2.546</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5029</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1347</v>
+        <v>0.3029</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3682</v>
+        <v>0.4316</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2742</v>
+        <v>-0.8837</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3905</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-0.8837</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ BUCETA</t>
+          <t>M. GIL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9744</v>
+        <v>-2.9243</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5506</v>
+        <v>-3.864</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5762</v>
+        <v>0.9397</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.002</v>
+        <v>0.1683</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.2144</v>
+        <v>0.9766</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2125</v>
+        <v>-0.8083</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.404</v>
+        <v>1.2881</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9239000000000001</v>
+        <v>2.4004</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4802</v>
+        <v>-1.1123</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5979</v>
+        <v>-1.1198</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2905</v>
+        <v>-1.4239</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6926</v>
+        <v>0.304</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3917</v>
+        <v>-2.546</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9377</v>
+        <v>-4.8962</v>
       </c>
       <c r="R11" t="n">
-        <v>2.546</v>
+        <v>2.3502</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3029</v>
+        <v>0.7277</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2088</v>
+        <v>0.1347</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5117</v>
+        <v>0.593</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.8837</v>
+        <v>-1.2742</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.3905</v>
       </c>
       <c r="X11" t="n">
         <v>-0.8837</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2493</v>
+        <v>-3.3737</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1312</v>
+        <v>-2.3359</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.118</v>
+        <v>-1.0378</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0663</v>
@@ -1390,13 +1390,13 @@
         <v>1.3709</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1841</v>
+        <v>-0.3086</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0882</v>
+        <v>-0.1165</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2724</v>
+        <v>-0.1922</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3905</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.763700000000002</v>
+        <v>5.763699999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>8.563499999999998</v>
+        <v>8.5634</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7995</v>
+        <v>-2.7997</v>
       </c>
       <c r="G13" t="n">
         <v>5.041500000000001</v>
@@ -1459,7 +1459,7 @@
         <v>-2.5215</v>
       </c>
       <c r="P13" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>-1.665334536937735e-16</v>
       </c>
       <c r="Q13" t="n">
         <v>-14.6885</v>
@@ -1468,7 +1468,7 @@
         <v>14.6883</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9379</v>
+        <v>2.9377</v>
       </c>
       <c r="T13" t="n">
         <v>1.532</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.151</v>
+        <v>3.6655</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7117</v>
+        <v>5.2234</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5607</v>
+        <v>-1.5579</v>
       </c>
       <c r="G14" t="n">
         <v>2.2343</v>
@@ -1546,13 +1546,13 @@
         <v>2.546</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9254</v>
+        <v>-0.411</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8446</v>
+        <v>-0.3329</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0809</v>
+        <v>-0.0781</v>
       </c>
       <c r="V14" t="n">
         <v>0.2754</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9315</v>
+        <v>2.3755</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6199</v>
+        <v>2.9036</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6884</v>
+        <v>-0.528</v>
       </c>
       <c r="G15" t="n">
         <v>1.3824</v>
@@ -1624,13 +1624,13 @@
         <v>1.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>0.041</v>
+        <v>-0.5149</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0257</v>
+        <v>0.3094</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9847</v>
+        <v>-0.8243</v>
       </c>
       <c r="V15" t="n">
         <v>0.3329</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2712</v>
+        <v>2.2518</v>
       </c>
       <c r="E16" t="n">
-        <v>2.17</v>
+        <v>2.0676</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1012</v>
+        <v>0.1842</v>
       </c>
       <c r="G16" t="n">
         <v>0.0716</v>
@@ -1702,13 +1702,13 @@
         <v>2.1543</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0832</v>
+        <v>0.0638</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.09</v>
+        <v>-0.1923</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1732</v>
+        <v>0.2561</v>
       </c>
       <c r="V16" t="n">
         <v>0.9412</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. CISSOKO</t>
+          <t>D. MARTIN MACEIRA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.6233</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2288</v>
+        <v>1.0617</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2918</v>
+        <v>-0.4384</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2843</v>
+        <v>-3.0639</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2743</v>
+        <v>-1.4366</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.99</v>
+        <v>-1.6274</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0812</v>
+        <v>0.2912</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0003</v>
+        <v>0.4643</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0808</v>
+        <v>-0.1732</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-3.3551</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2739</v>
+        <v>-1.9009</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0708</v>
+        <v>-1.4542</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3917</v>
+        <v>2.1543</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2403</v>
+        <v>-0.2541</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1269</v>
+        <v>-0.3505</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1134</v>
+        <v>0.0965</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2.7662</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.1003</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. ACEVEDO VASQUEZ</t>
+          <t>M. CISSOKO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.0114</v>
       </c>
       <c r="E18" t="n">
-        <v>3.378</v>
+        <v>0.4101</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.7102</v>
+        <v>-0.3987</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3327</v>
+        <v>0.2843</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6056</v>
+        <v>1.2743</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2729</v>
+        <v>-0.99</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2796</v>
+        <v>1.0812</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7597</v>
+        <v>1.0003</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4802</v>
+        <v>0.0808</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9468</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1541</v>
+        <v>0.2739</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7927</v>
+        <v>-1.0708</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7834</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1751</v>
+        <v>0.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0021</v>
+        <v>0.3147</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1733</v>
+        <v>0.3082</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1712</v>
+        <v>0.0065</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8837</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8837</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7673</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MARTIN MACEIRA</t>
+          <t>R. ACEVEDO VASQUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5595</v>
+        <v>-0.0707</v>
       </c>
       <c r="E19" t="n">
-        <v>0.55</v>
+        <v>2.5594</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1095</v>
+        <v>-2.63</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.0639</v>
+        <v>1.3327</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4366</v>
+        <v>2.6056</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6274</v>
+        <v>-1.2729</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2912</v>
+        <v>3.2796</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4643</v>
+        <v>3.7597</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1732</v>
+        <v>-0.4802</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.3551</v>
+        <v>-1.9468</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9009</v>
+        <v>-1.1541</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4542</v>
+        <v>-0.7927</v>
       </c>
       <c r="P19" t="n">
+        <v>-0.7834</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-1.9585</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.1751</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-0.9792</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.1543</v>
-      </c>
       <c r="S19" t="n">
-        <v>-1.4368</v>
+        <v>0.2636</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8622</v>
+        <v>0.3546</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5746</v>
+        <v>-0.091</v>
       </c>
       <c r="V19" t="n">
-        <v>2.7662</v>
+        <v>-0.8837</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1003</v>
+        <v>0.8837</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6659</v>
+        <v>-1.7673</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8179</v>
+        <v>-1.8003</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6023</v>
+        <v>-1.3976</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2156</v>
+        <v>-0.4027</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5582</v>
@@ -2014,13 +2014,13 @@
         <v>0.9792</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6882</v>
+        <v>-0.6706</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6358</v>
+        <v>-0.4311</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0524</v>
+        <v>-0.2395</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5507</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0465</v>
+        <v>-1.993</v>
       </c>
       <c r="E21" t="n">
         <v>-1.7425</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3039</v>
+        <v>-0.2505</v>
       </c>
       <c r="G21" t="n">
         <v>-0.399</v>
@@ -2092,13 +2092,13 @@
         <v>0.1958</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1602</v>
+        <v>-0.1067</v>
       </c>
       <c r="T21" t="n">
         <v>-0.0594</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1008</v>
+        <v>-0.0473</v>
       </c>
       <c r="V21" t="n">
         <v>0.2754</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2687</v>
+        <v>-4.9017</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.2891</v>
+        <v>-3.4704</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9797</v>
+        <v>-1.4313</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9964</v>
@@ -2170,13 +2170,13 @@
         <v>2.3502</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7643</v>
+        <v>-0.3973</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.408</v>
+        <v>-0.5893</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6437</v>
+        <v>0.192</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9412</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.0297</v>
+        <v>-5.2434</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2249</v>
+        <v>-4.8155</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.4278</v>
       </c>
       <c r="G23" t="n">
         <v>-3.3294</v>
@@ -2248,13 +2248,13 @@
         <v>1.5668</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3294</v>
+        <v>-0.543</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8316</v>
+        <v>-0.4223</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4977</v>
+        <v>-0.1207</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.763800000000001</v>
+        <v>-5.081600000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>2.7996</v>
+        <v>2.799799999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.563500000000001</v>
+        <v>-7.881100000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.041599999999999</v>
+        <v>-5.0416</v>
       </c>
       <c r="H24" t="n">
         <v>1.0208</v>
@@ -2326,13 +2326,13 @@
         <v>14.6885</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.9377</v>
+        <v>-2.2555</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.4057</v>
+        <v>-1.4056</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.532</v>
+        <v>-0.8498000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>2.2155</v>
